--- a/Pat_cummins_Data.xlsx
+++ b/Pat_cummins_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2dfaeb74ab2bd9f2/Desktop/exl_database/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2dfaeb74ab2bd9f2/Desktop/exl_database/PatCummins_Stats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{58DD04FB-8A49-4645-8437-001013CE310F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4B3A3BC-25F2-4420-8028-19DD15207CC1}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{C98E9005-8231-4581-9B7D-6E4FB601EC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6CBD200-A722-43CE-A26B-362632465D08}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DC078C0A-510E-4C91-B8B9-C7B9E188C4A5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{DC078C0A-510E-4C91-B8B9-C7B9E188C4A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Batting" sheetId="1" r:id="rId1"/>
@@ -125,9 +125,6 @@
     <t>5/57</t>
   </si>
   <si>
-    <t>3/44</t>
-  </si>
-  <si>
     <t>3/28</t>
   </si>
   <si>
@@ -195,6 +192,9 @@
   </si>
   <si>
     <t>T20I</t>
+  </si>
+  <si>
+    <t>6/28</t>
   </si>
 </sst>
 </file>
@@ -293,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -335,11 +335,14 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -706,8 +709,8 @@
       <c r="N2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="18" t="s">
-        <v>48</v>
+      <c r="O2" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -751,7 +754,7 @@
         <v>68.2</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -795,7 +798,7 @@
         <v>81.900000000000006</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -839,7 +842,7 @@
         <v>80.8</v>
       </c>
       <c r="O5" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -883,7 +886,7 @@
         <v>83.9</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -927,7 +930,7 @@
         <v>84.1</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -971,7 +974,7 @@
         <v>74.8</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1015,7 +1018,7 @@
         <v>71.7</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1059,7 +1062,7 @@
         <v>75.900000000000006</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1103,51 +1106,51 @@
         <v>70.5</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="7">
+      <c r="B12" s="19">
         <v>2025</v>
       </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1">
-        <v>10</v>
-      </c>
-      <c r="E12" s="1">
-        <v>20</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>50</v>
-      </c>
-      <c r="I12" s="1">
-        <v>10</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>65</v>
+      <c r="C12" s="18">
+        <v>6</v>
+      </c>
+      <c r="D12" s="18">
+        <v>71</v>
+      </c>
+      <c r="E12" s="18">
+        <v>83</v>
+      </c>
+      <c r="F12" s="18">
+        <v>6</v>
+      </c>
+      <c r="G12" s="18">
+        <v>11.83</v>
+      </c>
+      <c r="H12" s="18">
+        <v>85.54</v>
+      </c>
+      <c r="I12" s="18">
+        <v>28</v>
+      </c>
+      <c r="J12" s="18">
+        <v>0</v>
+      </c>
+      <c r="K12" s="18">
+        <v>0</v>
+      </c>
+      <c r="L12" s="18">
+        <v>8</v>
+      </c>
+      <c r="M12" s="18">
+        <v>1</v>
+      </c>
+      <c r="N12" s="18">
+        <v>60.2</v>
       </c>
       <c r="O12" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1217,7 +1220,7 @@
         <v>10</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1261,7 +1264,7 @@
         <v>55.6</v>
       </c>
       <c r="O3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1305,7 +1308,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1349,7 +1352,7 @@
         <v>80</v>
       </c>
       <c r="O5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1393,7 +1396,7 @@
         <v>80</v>
       </c>
       <c r="O6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1437,7 +1440,7 @@
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1481,7 +1484,7 @@
         <v>56</v>
       </c>
       <c r="O8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1525,7 +1528,7 @@
         <v>62.7</v>
       </c>
       <c r="O9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1569,7 +1572,7 @@
         <v>50</v>
       </c>
       <c r="O10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1613,7 +1616,7 @@
         <v>49.2</v>
       </c>
       <c r="O11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1657,7 +1660,7 @@
         <v>52.9</v>
       </c>
       <c r="O12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1701,7 +1704,7 @@
         <v>63.6</v>
       </c>
       <c r="O13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1745,7 +1748,7 @@
         <v>60.4</v>
       </c>
       <c r="O14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1815,7 +1818,7 @@
         <v>10</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1859,7 +1862,7 @@
         <v>50</v>
       </c>
       <c r="O3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1903,7 +1906,7 @@
         <v>71.400000000000006</v>
       </c>
       <c r="O4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1947,7 +1950,7 @@
         <v>33.299999999999997</v>
       </c>
       <c r="O5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1991,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2035,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2079,7 +2082,7 @@
         <v>33.299999999999997</v>
       </c>
       <c r="O8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2123,7 +2126,7 @@
         <v>38.799999999999997</v>
       </c>
       <c r="O9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2167,7 +2170,7 @@
         <v>48.7</v>
       </c>
       <c r="O10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2241,7 +2244,7 @@
         <v>18</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2285,7 +2288,7 @@
         <v>80.7</v>
       </c>
       <c r="O3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2329,7 +2332,7 @@
         <v>78.099999999999994</v>
       </c>
       <c r="O4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2373,7 +2376,7 @@
         <v>78.7</v>
       </c>
       <c r="O5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2417,7 +2420,7 @@
         <v>80.7</v>
       </c>
       <c r="O6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2461,7 +2464,7 @@
         <v>81</v>
       </c>
       <c r="O7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2505,7 +2508,7 @@
         <v>81.5</v>
       </c>
       <c r="O8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2549,7 +2552,7 @@
         <v>79.7</v>
       </c>
       <c r="O9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2593,7 +2596,7 @@
         <v>70.7</v>
       </c>
       <c r="O10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2637,7 +2640,7 @@
         <v>75</v>
       </c>
       <c r="O11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2645,64 +2648,64 @@
         <v>2025</v>
       </c>
       <c r="C12" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>30.2</v>
+        <v>84.1</v>
       </c>
       <c r="E12" s="1">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="F12" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="H12" s="1">
-        <v>16.2</v>
+        <v>22.55</v>
       </c>
       <c r="I12" s="1">
-        <v>36.4</v>
+        <v>45.7</v>
       </c>
       <c r="J12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="L12" s="1">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M12" s="1">
         <v>1</v>
       </c>
       <c r="N12" s="1">
-        <v>79.099999999999994</v>
+        <v>50</v>
       </c>
       <c r="O12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="K3 K5:K12" twoDigitTextYear="1"/>
+    <ignoredError sqref="K3 K5:K11" twoDigitTextYear="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2757,7 +2760,7 @@
         <v>18</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2789,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M3" s="1">
         <v>18</v>
@@ -2801,7 +2804,7 @@
         <v>55.1</v>
       </c>
       <c r="P3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2833,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M4" s="1">
         <v>6</v>
@@ -2845,7 +2848,7 @@
         <v>56.4</v>
       </c>
       <c r="P4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2877,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M5" s="1">
         <v>16</v>
@@ -2889,7 +2892,7 @@
         <v>61.4</v>
       </c>
       <c r="P5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2921,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M6" s="1">
         <v>54</v>
@@ -2933,7 +2936,7 @@
         <v>61.4</v>
       </c>
       <c r="P6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2965,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M7" s="1">
         <v>16</v>
@@ -2977,7 +2980,7 @@
         <v>55.9</v>
       </c>
       <c r="P7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3009,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M8" s="1">
         <v>70</v>
@@ -3021,7 +3024,7 @@
         <v>58</v>
       </c>
       <c r="P8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3053,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M9" s="1">
         <v>22</v>
@@ -3065,7 +3068,7 @@
         <v>66.400000000000006</v>
       </c>
       <c r="P9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3097,7 +3100,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M10" s="1">
         <v>72</v>
@@ -3109,7 +3112,7 @@
         <v>64.7</v>
       </c>
       <c r="P10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3141,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M11" s="1">
         <v>60</v>
@@ -3153,7 +3156,7 @@
         <v>59.5</v>
       </c>
       <c r="P11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3185,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M12" s="1">
         <v>22</v>
@@ -3197,7 +3200,7 @@
         <v>66.599999999999994</v>
       </c>
       <c r="P12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3229,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M13" s="1">
         <v>58</v>
@@ -3241,7 +3244,7 @@
         <v>52.2</v>
       </c>
       <c r="P13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3273,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M14" s="1">
         <v>6</v>
@@ -3285,7 +3288,7 @@
         <v>59</v>
       </c>
       <c r="P14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3362,7 +3365,7 @@
         <v>18</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3394,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M3" s="1">
         <v>6</v>
@@ -3406,7 +3409,7 @@
         <v>60.4</v>
       </c>
       <c r="P3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3438,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M4" s="1">
         <v>33</v>
@@ -3450,7 +3453,7 @@
         <v>49.5</v>
       </c>
       <c r="P4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3482,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M5" s="1">
         <v>1</v>
@@ -3494,7 +3497,7 @@
         <v>50</v>
       </c>
       <c r="P5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3526,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" s="1">
         <v>1</v>
@@ -3538,7 +3541,7 @@
         <v>50</v>
       </c>
       <c r="P6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3570,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M7" s="1">
         <v>11</v>
@@ -3582,7 +3585,7 @@
         <v>48.3</v>
       </c>
       <c r="P7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3614,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M8" s="1">
         <v>13</v>
@@ -3626,7 +3629,7 @@
         <v>41.7</v>
       </c>
       <c r="P8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3658,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M9" s="1">
         <v>11</v>
@@ -3670,7 +3673,7 @@
         <v>36.700000000000003</v>
       </c>
       <c r="P9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3702,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M10" s="1">
         <v>16</v>
@@ -3714,7 +3717,7 @@
         <v>47.2</v>
       </c>
       <c r="P10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3746,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M11" s="1">
         <v>43</v>
@@ -3758,7 +3761,7 @@
         <v>51.7</v>
       </c>
       <c r="P11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3790,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M12" s="1">
         <v>15</v>
@@ -3802,7 +3805,7 @@
         <v>44.2</v>
       </c>
       <c r="P12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
